--- a/HR Capstone Completed Rashida Yakubu.xlsx
+++ b/HR Capstone Completed Rashida Yakubu.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
-  <workbookPr hidePivotFieldList="1"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RASHIDA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RASHIDA\Desktop\HR_Capstone_Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43087281-3B5A-4532-8A78-7DB493CC8435}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{164ED245-2DD4-44F7-869B-2E8992EE888F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -85,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1547" uniqueCount="444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1549" uniqueCount="446">
   <si>
     <t>Dept Code</t>
   </si>
@@ -1417,6 +1417,12 @@
   </si>
   <si>
     <t>Actual Pay</t>
+  </si>
+  <si>
+    <t>Column Labels</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
   </si>
 </sst>
 </file>
@@ -1597,7 +1603,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1635,13 +1641,12 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="32">
+  <dxfs count="28">
     <dxf>
       <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
     </dxf>
@@ -1826,10 +1831,7 @@
       </font>
     </dxf>
     <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="9" formatCode="&quot;$&quot;#,##0_);\(&quot;$&quot;#,##0\)"/>
+      <numFmt numFmtId="13" formatCode="0%"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
@@ -1838,19 +1840,10 @@
       <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
+      <numFmt numFmtId="9" formatCode="&quot;$&quot;#,##0_);\(&quot;$&quot;#,##0\)"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
@@ -2399,22 +2392,22 @@
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
+                  <c:v>Operations</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>Information Technology</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>Sales</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>Operations</c:v>
+                <c:pt idx="3">
+                  <c:v>Finance</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>Marketing</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>Human Resources</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Finance</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2426,22 +2419,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>34</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>29</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>24</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>19</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>17</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>17</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2517,22 +2510,22 @@
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
+                  <c:v>Operations</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>Information Technology</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>Sales</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>Operations</c:v>
+                <c:pt idx="3">
+                  <c:v>Finance</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>Marketing</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>Human Resources</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Finance</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2544,22 +2537,22 @@
                 <c:formatCode>_("$"* #,##0_);_("$"* \(#,##0\);_("$"* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>78738.441176470587</c:v>
+                  <c:v>67739.833333333328</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>82899.137931034478</c:v>
+                  <c:v>81264.833333333328</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>75290.416666666672</c:v>
+                  <c:v>75379.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>84821.263157894733</c:v>
+                  <c:v>67195</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>86878.76470588235</c:v>
+                  <c:v>86729</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>85206.470588235301</c:v>
+                  <c:v>109408</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3389,6 +3382,32 @@
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="12"/>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:delete val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="13"/>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:delete val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
       <c:layout>
@@ -3411,11 +3430,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Analysis!$G$6</c:f>
+              <c:f>Analysis!$G$6:$G$7</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Total</c:v>
+                  <c:v>Left</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3423,7 +3442,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Analysis!$F$7:$F$13</c:f>
+              <c:f>Analysis!$F$8:$F$14</c:f>
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
@@ -3449,27 +3468,27 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Analysis!$G$7:$G$13</c:f>
+              <c:f>Analysis!$G$8:$G$14</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0.12142857142857143</c:v>
+                  <c:v>0.125</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.12142857142857143</c:v>
+                  <c:v>8.3333333333333329E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.24285714285714285</c:v>
+                  <c:v>0.25</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.1357142857142857</c:v>
+                  <c:v>0.125</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.17142857142857143</c:v>
+                  <c:v>0.25</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.20714285714285716</c:v>
+                  <c:v>0.16666666666666666</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4115,9 +4134,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Analysis!$K$8:$K$13</c:f>
+              <c:f>Analysis!$K$8:$K$12</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>Exceeding</c:v>
                 </c:pt>
@@ -4125,12 +4144,9 @@
                   <c:v>Achieving</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Outstanding</c:v>
+                  <c:v>Developing</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Developing</c:v>
-                </c:pt>
-                <c:pt idx="4">
                   <c:v>Needs Improvement</c:v>
                 </c:pt>
               </c:strCache>
@@ -4138,23 +4154,20 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Analysis!$L$8:$L$13</c:f>
+              <c:f>Analysis!$L$8:$L$12</c:f>
               <c:numCache>
                 <c:formatCode>_("$"* #,##0_);_("$"* \(#,##0\);_("$"* "-"??_);_(@_)</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>1316600.7999999998</c:v>
+                  <c:v>169403.2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>160371.40000000002</c:v>
+                  <c:v>41189.799999999996</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>91073.88</c:v>
+                  <c:v>10882.46</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>69012.42</c:v>
-                </c:pt>
-                <c:pt idx="4">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -4315,8 +4328,8 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[HR Capstone Completed Rashida Yakubu.xlsx]Analysis!PivotTable9</c:name>
-    <c:fmtId val="12"/>
+    <c:name>[HR Capstone Completed Rashida Yakubu.xlsx]Analysis!PivotTable5</c:name>
+    <c:fmtId val="10"/>
   </c:pivotSource>
   <c:chart>
     <c:title>
@@ -4339,7 +4352,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1400" b="1">
+              <a:rPr lang="en-US" b="1">
                 <a:solidFill>
                   <a:schemeClr val="accent6">
                     <a:lumMod val="50000"/>
@@ -4349,7 +4362,7 @@
               <a:t>PERFORMANCE</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-US" sz="1400" b="1" baseline="0">
+              <a:rPr lang="en-US" b="1" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="accent6">
                     <a:lumMod val="50000"/>
@@ -4358,6 +4371,13 @@
               </a:rPr>
               <a:t> BY STATUS</a:t>
             </a:r>
+            <a:endParaRPr lang="en-US" b="1">
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:endParaRPr>
           </a:p>
         </c:rich>
       </c:tx>
@@ -4394,10 +4414,123 @@
     <c:pivotFmts>
       <c:pivotFmt>
         <c:idx val="0"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent6">
+                  <a:tint val="50000"/>
+                  <a:satMod val="300000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="35000">
+                <a:schemeClr val="accent6">
+                  <a:tint val="37000"/>
+                  <a:satMod val="300000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent6">
+                  <a:tint val="15000"/>
+                  <a:satMod val="350000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="16200000" scaled="1"/>
+          </a:gradFill>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="accent6">
+                <a:shade val="95000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="4"/>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="50000"/>
+                    <a:satMod val="300000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="35000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="37000"/>
+                    <a:satMod val="300000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="15000"/>
+                    <a:satMod val="350000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="16200000" scaled="1"/>
+            </a:gradFill>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:shade val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="38000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+        </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="accent6">
+                      <a:lumMod val="50000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
@@ -4409,81 +4542,6 @@
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="1"/>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="2"/>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="3"/>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="4"/>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="5"/>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="6"/>
         <c:spPr>
           <a:gradFill rotWithShape="1">
             <a:gsLst>
@@ -4543,11 +4601,10 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="tx1">
+                    <a:schemeClr val="accent6">
                       <a:lumMod val="50000"/>
-                      <a:lumOff val="50000"/>
                     </a:schemeClr>
                   </a:solidFill>
                   <a:latin typeface="+mn-lt"/>
@@ -4571,7 +4628,7 @@
         </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
-        <c:idx val="7"/>
+        <c:idx val="2"/>
         <c:spPr>
           <a:gradFill rotWithShape="1">
             <a:gsLst>
@@ -4631,102 +4688,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="50000"/>
-                      <a:lumOff val="50000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="outEnd"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="8"/>
-        <c:spPr>
-          <a:gradFill rotWithShape="1">
-            <a:gsLst>
-              <a:gs pos="0">
-                <a:schemeClr val="accent6">
-                  <a:tint val="50000"/>
-                  <a:satMod val="300000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="35000">
-                <a:schemeClr val="accent6">
-                  <a:tint val="37000"/>
-                  <a:satMod val="300000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="100000">
-                <a:schemeClr val="accent6">
-                  <a:tint val="15000"/>
-                  <a:satMod val="350000"/>
-                </a:schemeClr>
-              </a:gs>
-            </a:gsLst>
-            <a:lin ang="16200000" scaled="1"/>
-          </a:gradFill>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="accent6">
-                <a:shade val="95000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:ln w="19050">
-                    <a:solidFill>
-                      <a:schemeClr val="accent6">
-                        <a:lumMod val="50000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                  </a:ln>
+                <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="accent6">
                       <a:lumMod val="50000"/>
@@ -4759,10 +4721,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="4.953061417961583E-2"/>
-          <c:y val="0.14659685863874344"/>
-          <c:w val="0.91617896061911164"/>
-          <c:h val="0.72197296387766619"/>
+          <c:x val="2.1814091263844686E-2"/>
+          <c:y val="0.14856481481481484"/>
+          <c:w val="0.93888888888888888"/>
+          <c:h val="0.72088764946048411"/>
         </c:manualLayout>
       </c:layout>
       <c:barChart>
@@ -4774,7 +4736,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Analysis!$B$32</c:f>
+              <c:f>Analysis!$B$33</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4833,20 +4795,13 @@
               <a:effectLst/>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:ln w="19050">
-                      <a:solidFill>
-                        <a:schemeClr val="accent6">
-                          <a:lumMod val="50000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                    </a:ln>
+                  <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="accent6">
                         <a:lumMod val="50000"/>
@@ -4889,7 +4844,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Analysis!$A$33:$A$35</c:f>
+              <c:f>Analysis!$A$34:$A$36</c:f>
               <c:strCache>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
@@ -4903,7 +4858,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Analysis!$B$33:$B$35</c:f>
+              <c:f>Analysis!$B$34:$B$36</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="2"/>
@@ -4918,7 +4873,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-F0FE-4C2A-A32F-D9C6C191C6A9}"/>
+              <c16:uniqueId val="{00000000-56B9-45B6-ADB6-40CDBF4E83DB}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4933,11 +4888,11 @@
         </c:dLbls>
         <c:gapWidth val="100"/>
         <c:overlap val="-24"/>
-        <c:axId val="1280651711"/>
-        <c:axId val="1280654111"/>
+        <c:axId val="302389391"/>
+        <c:axId val="302397551"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1280651711"/>
+        <c:axId val="302389391"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4965,7 +4920,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="accent6">
                     <a:lumMod val="50000"/>
@@ -4979,7 +4934,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1280654111"/>
+        <c:crossAx val="302397551"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4987,17 +4942,17 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1280654111"/>
+        <c:axId val="302397551"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="1"/>
         <c:axPos val="l"/>
         <c:numFmt formatCode="0" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="1280651711"/>
+        <c:crossAx val="302389391"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5012,7 +4967,13 @@
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
-    <c:extLst/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
   </c:chart>
   <c:spPr>
     <a:noFill/>
@@ -5254,22 +5215,22 @@
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
+                  <c:v>Operations</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>Information Technology</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>Sales</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>Operations</c:v>
+                <c:pt idx="3">
+                  <c:v>Finance</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>Marketing</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>Human Resources</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Finance</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5281,22 +5242,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>34</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>29</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>24</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>19</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>17</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>17</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5372,22 +5333,22 @@
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
+                  <c:v>Operations</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>Information Technology</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>Sales</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>Operations</c:v>
+                <c:pt idx="3">
+                  <c:v>Finance</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>Marketing</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>Human Resources</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Finance</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5399,22 +5360,22 @@
                 <c:formatCode>_("$"* #,##0_);_("$"* \(#,##0\);_("$"* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>78738.441176470587</c:v>
+                  <c:v>67739.833333333328</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>82899.137931034478</c:v>
+                  <c:v>81264.833333333328</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>75290.416666666672</c:v>
+                  <c:v>75379.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>84821.263157894733</c:v>
+                  <c:v>67195</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>86878.76470588235</c:v>
+                  <c:v>86729</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>85206.470588235301</c:v>
+                  <c:v>109408</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6220,6 +6181,86 @@
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="10"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent6"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="11"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent6"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
       <c:layout>
@@ -6242,11 +6283,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Analysis!$G$6</c:f>
+              <c:f>Analysis!$G$6:$G$7</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Total</c:v>
+                  <c:v>Left</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6263,7 +6304,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Analysis!$F$7:$F$13</c:f>
+              <c:f>Analysis!$F$8:$F$14</c:f>
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
@@ -6289,27 +6330,27 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Analysis!$G$7:$G$13</c:f>
+              <c:f>Analysis!$G$8:$G$14</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0.12142857142857143</c:v>
+                  <c:v>0.125</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.12142857142857143</c:v>
+                  <c:v>8.3333333333333329E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.24285714285714285</c:v>
+                  <c:v>0.25</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.1357142857142857</c:v>
+                  <c:v>0.125</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.17142857142857143</c:v>
+                  <c:v>0.25</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.20714285714285716</c:v>
+                  <c:v>0.16666666666666666</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6461,7 +6502,7 @@
           <c:yMode val="edge"/>
           <c:x val="0.19227361421704989"/>
           <c:y val="0.82194095032726711"/>
-          <c:w val="0.11505129389453567"/>
+          <c:w val="0.11584469353909126"/>
           <c:h val="9.5930923504226648E-2"/>
         </c:manualLayout>
       </c:layout>
@@ -6548,718 +6589,6 @@
 </file>
 
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="108"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="8"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:pivotSource>
-    <c:name>[HR Capstone Completed Rashida Yakubu.xlsx]Analysis!PivotTable9</c:name>
-    <c:fmtId val="0"/>
-  </c:pivotSource>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="20" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="50000"/>
-                    <a:lumOff val="50000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" b="1">
-                <a:solidFill>
-                  <a:schemeClr val="accent6">
-                    <a:lumMod val="50000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>Performance by Status</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="20" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="50000"/>
-                  <a:lumOff val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:pivotFmts>
-      <c:pivotFmt>
-        <c:idx val="0"/>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="1"/>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="2"/>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="3"/>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="4"/>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="5"/>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="6"/>
-        <c:spPr>
-          <a:gradFill rotWithShape="1">
-            <a:gsLst>
-              <a:gs pos="0">
-                <a:schemeClr val="accent6">
-                  <a:tint val="50000"/>
-                  <a:satMod val="300000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="35000">
-                <a:schemeClr val="accent6">
-                  <a:tint val="37000"/>
-                  <a:satMod val="300000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="100000">
-                <a:schemeClr val="accent6">
-                  <a:tint val="15000"/>
-                  <a:satMod val="350000"/>
-                </a:schemeClr>
-              </a:gs>
-            </a:gsLst>
-            <a:lin ang="16200000" scaled="1"/>
-          </a:gradFill>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="accent6">
-                <a:shade val="95000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="50000"/>
-                      <a:lumOff val="50000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="outEnd"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-    </c:pivotFmts>
-    <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="4.953061417961583E-2"/>
-          <c:y val="0.14659685863874344"/>
-          <c:w val="0.91617896061911164"/>
-          <c:h val="0.61454205658847616"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Analysis!$B$32</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Total</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:gradFill rotWithShape="1">
-              <a:gsLst>
-                <a:gs pos="0">
-                  <a:schemeClr val="accent6">
-                    <a:tint val="50000"/>
-                    <a:satMod val="300000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="35000">
-                  <a:schemeClr val="accent6">
-                    <a:tint val="37000"/>
-                    <a:satMod val="300000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="100000">
-                  <a:schemeClr val="accent6">
-                    <a:tint val="15000"/>
-                    <a:satMod val="350000"/>
-                  </a:schemeClr>
-                </a:gs>
-              </a:gsLst>
-              <a:lin ang="16200000" scaled="1"/>
-            </a:gradFill>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="accent6">
-                  <a:shade val="95000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst>
-              <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-                <a:srgbClr val="000000">
-                  <a:alpha val="38000"/>
-                </a:srgbClr>
-              </a:outerShdw>
-            </a:effectLst>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="50000"/>
-                        <a:lumOff val="50000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="outEnd"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Analysis!$A$33:$A$35</c:f>
-              <c:strCache>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>Active</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Left</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Analysis!$B$33:$B$35</c:f>
-              <c:numCache>
-                <c:formatCode>0</c:formatCode>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>67.577586206896555</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>67.25</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-B620-45FF-AB1D-DD9894C0CAE0}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:dLblPos val="outEnd"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="100"/>
-        <c:overlap val="-24"/>
-        <c:axId val="1280651711"/>
-        <c:axId val="1280654111"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="1280651711"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="50000"/>
-                        <a:lumOff val="50000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US">
-                    <a:solidFill>
-                      <a:schemeClr val="accent6">
-                        <a:lumMod val="50000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>Employment</a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="en-US" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="accent6">
-                        <a:lumMod val="50000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t> status</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="50000"/>
-                      <a:lumOff val="50000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="50000"/>
-                    <a:lumOff val="50000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1280654111"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="1280654111"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="1"/>
-        <c:axPos val="l"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="50000"/>
-                        <a:lumOff val="50000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US">
-                    <a:solidFill>
-                      <a:schemeClr val="accent6">
-                        <a:lumMod val="50000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>performance</a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="en-US" baseline="0"/>
-                  <a:t> </a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="en-US" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="accent6">
-                        <a:lumMod val="50000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>average</a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t> </a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="50000"/>
-                      <a:lumOff val="50000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="0" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="1280651711"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-  <c:extLst>
-    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
-      <c14:pivotOptions>
-        <c14:dropZoneFilter val="1"/>
-        <c14:dropZonesVisible val="1"/>
-      </c14:pivotOptions>
-    </c:ext>
-    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
-      <c16:pivotOptions16>
-        <c16:showExpandCollapseFieldButtons val="1"/>
-      </c16:pivotOptions16>
-    </c:ext>
-  </c:extLst>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -7500,9 +6829,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Analysis!$K$8:$K$13</c:f>
+              <c:f>Analysis!$K$8:$K$12</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>Exceeding</c:v>
                 </c:pt>
@@ -7510,12 +6839,9 @@
                   <c:v>Achieving</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Outstanding</c:v>
+                  <c:v>Developing</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Developing</c:v>
-                </c:pt>
-                <c:pt idx="4">
                   <c:v>Needs Improvement</c:v>
                 </c:pt>
               </c:strCache>
@@ -7523,23 +6849,20 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Analysis!$L$8:$L$13</c:f>
+              <c:f>Analysis!$L$8:$L$12</c:f>
               <c:numCache>
                 <c:formatCode>_("$"* #,##0_);_("$"* \(#,##0\);_("$"* "-"??_);_(@_)</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>1316600.7999999998</c:v>
+                  <c:v>169403.2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>160371.40000000002</c:v>
+                  <c:v>41189.799999999996</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>91073.88</c:v>
+                  <c:v>10882.46</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>69012.42</c:v>
-                </c:pt>
-                <c:pt idx="4">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -7824,6 +7147,629 @@
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
     <c:extLst/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="108"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="8"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[HR Capstone Completed Rashida Yakubu.xlsx]Analysis!PivotTable5</c:name>
+    <c:fmtId val="11"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="20" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="50000"/>
+                    <a:lumOff val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" b="1">
+                <a:solidFill>
+                  <a:schemeClr val="accent6">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>PERFORMANCE</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" b="1" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="accent6">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:rPr>
+              <a:t> BY STATUS</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" b="1">
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="20" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="50000"/>
+                  <a:lumOff val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent6">
+                  <a:tint val="50000"/>
+                  <a:satMod val="300000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="35000">
+                <a:schemeClr val="accent6">
+                  <a:tint val="37000"/>
+                  <a:satMod val="300000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent6">
+                  <a:tint val="15000"/>
+                  <a:satMod val="350000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="16200000" scaled="1"/>
+          </a:gradFill>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="accent6">
+                <a:shade val="95000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="4"/>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="50000"/>
+                    <a:satMod val="300000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="35000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="37000"/>
+                    <a:satMod val="300000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="15000"/>
+                    <a:satMod val="350000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="16200000" scaled="1"/>
+            </a:gradFill>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:shade val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="38000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="50000"/>
+                      <a:lumOff val="50000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent6">
+                  <a:tint val="50000"/>
+                  <a:satMod val="300000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="35000">
+                <a:schemeClr val="accent6">
+                  <a:tint val="37000"/>
+                  <a:satMod val="300000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent6">
+                  <a:tint val="15000"/>
+                  <a:satMod val="350000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="16200000" scaled="1"/>
+          </a:gradFill>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="accent6">
+                <a:shade val="95000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="50000"/>
+                      <a:lumOff val="50000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="1.6800026468039842E-2"/>
+          <c:y val="0.14902762956127391"/>
+          <c:w val="0.93888888888888888"/>
+          <c:h val="0.72088764946048411"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Analysis!$B$33</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="50000"/>
+                    <a:satMod val="300000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="35000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="37000"/>
+                    <a:satMod val="300000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="15000"/>
+                    <a:satMod val="350000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="16200000" scaled="1"/>
+            </a:gradFill>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:shade val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="38000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="50000"/>
+                        <a:lumOff val="50000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Analysis!$A$34:$A$36</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Active</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Left</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Analysis!$B$34:$B$36</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>67.577586206896555</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>67.25</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9863-4EE2-AF41-3E6CE760B8A1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="100"/>
+        <c:overlap val="-24"/>
+        <c:axId val="302389391"/>
+        <c:axId val="302397551"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="302389391"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="accent6">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="302397551"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="302397551"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="302389391"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -10508,531 +10454,6 @@
 </file>
 
 <file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="206">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="50000"/>
-        <a:lumOff val="50000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200" cap="all"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="50000"/>
-        <a:lumOff val="50000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="50000"/>
-        <a:lumOff val="50000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="2">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="1"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:shade val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="2">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="1"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:shade val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="2">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="1"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="15875" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="2">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="1"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:shade val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="4"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="2"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="50000"/>
-        <a:lumOff val="50000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:prstDash val="dash"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:prstDash val="dash"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="50000"/>
-        <a:lumOff val="50000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="50000"/>
-        <a:lumOff val="50000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:prstDash val="dash"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="50000"/>
-        <a:lumOff val="50000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" kern="1200" cap="none" spc="20" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="2"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="50000"/>
-        <a:lumOff val="50000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="50000"/>
-        <a:lumOff val="50000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="210">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -11614,6 +11035,531 @@
       <a:schemeClr val="tx1">
         <a:lumMod val="65000"/>
         <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="206">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="1"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:shade val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="1"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:shade val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="1"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="15875" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="1"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:shade val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="4"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" kern="1200" cap="none" spc="20" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -12396,7 +12342,7 @@
               <a:cs typeface="Calibri"/>
             </a:rPr>
             <a:pPr algn="l"/>
-            <a:t>24%</a:t>
+            <a:t>25%</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="3200" b="1">
             <a:solidFill>
@@ -13454,44 +13400,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>432956</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>34636</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>119063</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>149679</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="42" name="Chart 41">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2100C2A1-B7C5-4EE8-9984-17539CAC1A63}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>18</xdr:col>
       <xdr:colOff>312963</xdr:colOff>
       <xdr:row>20</xdr:row>
@@ -13516,8 +13424,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="11334749" y="4026938"/>
-          <a:ext cx="2109108" cy="4164561"/>
+          <a:off x="11171463" y="4022402"/>
+          <a:ext cx="2081894" cy="4164561"/>
           <a:chOff x="11334749" y="5225144"/>
           <a:chExt cx="2068286" cy="2830286"/>
         </a:xfrm>
@@ -13744,7 +13652,7 @@
                   </a:schemeClr>
                 </a:solidFill>
               </a:rPr>
-              <a:t>Information Technology has the highest attrition rate.</a:t>
+              <a:t>Information Technology and Operations has the highest attrition rate.</a:t>
             </a:r>
           </a:p>
           <a:p>
@@ -13807,8 +13715,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="11566071" y="2177141"/>
-          <a:ext cx="1265464" cy="775609"/>
+          <a:off x="11402785" y="2172605"/>
+          <a:ext cx="1247321" cy="775609"/>
           <a:chOff x="11620499" y="2748643"/>
           <a:chExt cx="1279072" cy="966107"/>
         </a:xfrm>
@@ -13816,7 +13724,7 @@
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
           <xdr:cNvPr id="46" name="Oval 45">
-            <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+            <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                 <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2CA17F71-2B76-DA5B-2D82-A23DFB9B54E7}"/>
@@ -13861,7 +13769,7 @@
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
           <xdr:cNvPr id="48" name="TextBox 47">
-            <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+            <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                 <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5E9356BA-79BC-03C6-C980-B8ADED98828B}"/>
@@ -13950,8 +13858,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="11634107" y="2993571"/>
-          <a:ext cx="1170214" cy="721179"/>
+          <a:off x="11461750" y="2989035"/>
+          <a:ext cx="1161142" cy="721179"/>
           <a:chOff x="11707859" y="3813380"/>
           <a:chExt cx="1368605" cy="921906"/>
         </a:xfrm>
@@ -13959,7 +13867,7 @@
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
           <xdr:cNvPr id="51" name="Oval 50">
-            <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+            <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                 <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0688C599-0BA0-4E23-86C1-8F3DA7EE6172}"/>
@@ -14004,7 +13912,7 @@
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
           <xdr:cNvPr id="52" name="TextBox 51">
-            <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+            <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                 <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A79FE9C2-7D3F-44E1-9F38-7FB82E0B8983}"/>
@@ -14067,6 +13975,44 @@
     </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>367393</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>27214</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>108857</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="9" name="Chart 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F0346CA6-2630-4AD7-A156-BF2A7E18783B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -14111,15 +14057,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>24761</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>33544</xdr:rowOff>
+      <xdr:colOff>405761</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>89574</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>481853</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>172089</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>37619</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -14139,42 +14085,6 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>713</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>72837</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1871943</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>177612</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Chart 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CE015B30-A18F-3E52-268D-8D26256CA9CC}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -14210,7 +14120,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -14232,7 +14142,7 @@
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="21" name="Oval 20">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{49FB8EAF-DC05-4661-8D29-9A51259E56E5}"/>
@@ -14292,7 +14202,7 @@
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="23" name="TextBox 22">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7804141-0C38-0003-9B57-2F3B2CC51D35}"/>
@@ -14370,7 +14280,7 @@
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="26" name="Oval 25">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BA1849C4-48AF-224A-B02B-40F8D0DE7260}"/>
@@ -14429,7 +14339,7 @@
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="27" name="TextBox 26">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FA7348CC-A4F2-459B-7BAF-9B5C2B2E5952}"/>
@@ -14572,6 +14482,42 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>17318</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>121227</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="8" name="Chart 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD0795CC-503C-7D12-A82A-90B142CAEF50}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -17226,159 +17172,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A03E8F95-B095-4BA2-B206-DC1E62353E55}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="15" rowHeaderCaption="Employment Status">
-  <location ref="L32:L33" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="14">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="4"/>
-        <item x="5"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item h="1" x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="1"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Employee ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="23">
-      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleDark7" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{61ECD8DF-09A4-4D16-A406-F0081E1DC1AA}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="15" rowHeaderCaption="Employment Status">
-  <location ref="J33:J34" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="14">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="4"/>
-        <item x="5"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item h="1" x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="1"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Salary" fld="6" baseField="0" baseItem="0" numFmtId="5"/>
-  </dataFields>
-  <formats count="2">
-    <format dxfId="25">
-      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="24">
-      <pivotArea outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleDark7" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{046CD93E-E41C-4D4F-9767-8EFFEE94BF47}" name="PivotTable10" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="17" rowHeaderCaption="Performance Band">
-  <location ref="K7:L13" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <location ref="K7:L12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -17401,7 +17196,7 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0">
       <items count="4">
-        <item x="0"/>
+        <item h="1" x="0"/>
         <item x="1"/>
         <item h="1" x="2"/>
         <item t="default"/>
@@ -17433,15 +17228,12 @@
   <rowFields count="1">
     <field x="10"/>
   </rowFields>
-  <rowItems count="6">
+  <rowItems count="5">
     <i>
       <x v="2"/>
     </i>
     <i>
       <x/>
-    </i>
-    <i>
-      <x v="4"/>
     </i>
     <i>
       <x v="1"/>
@@ -17491,156 +17283,9 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C74D3B32-7A66-495D-8E23-957FBE689175}" name="PivotTable9" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="21" rowHeaderCaption="Employment Status">
-  <location ref="A32:B35" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="14">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="4"/>
-        <item x="5"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item h="1" x="2"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="1"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="9"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Average of Performance Score" fld="7" subtotal="average" baseField="8" baseItem="0"/>
-  </dataFields>
-  <formats count="5">
-    <format dxfId="30">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="9" count="1">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="29">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="9" count="1">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="28">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="9" count="1">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="27">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="9" count="1">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="26">
-      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="2">
-    <chartFormat chart="0" format="6" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="12" format="8" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleDark7" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{155A8538-D781-4C2E-81BC-771EB4FF4A74}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="13" rowHeaderCaption="Departments">
-  <location ref="F6:G13" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <location ref="F6:H14" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
@@ -17661,9 +17306,9 @@
     <pivotField numFmtId="164" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField showAll="0" defaultSubtotal="0">
+    <pivotField axis="axisCol" showAll="0" defaultSubtotal="0">
       <items count="3">
-        <item x="0"/>
+        <item h="1" x="0"/>
         <item x="1"/>
         <item h="1" x="2"/>
       </items>
@@ -17708,8 +17353,16 @@
       <x/>
     </i>
   </rowItems>
-  <colItems count="1">
-    <i/>
+  <colFields count="1">
+    <field x="9"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
   </colItems>
   <dataFields count="1">
     <dataField name="Count of Employee ID" fld="0" subtotal="count" baseField="2" baseItem="0" numFmtId="9">
@@ -17721,11 +17374,11 @@
     </dataField>
   </dataFields>
   <formats count="1">
-    <format dxfId="31">
+    <format dxfId="23">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
-  <chartFormats count="2">
+  <chartFormats count="6">
     <chartFormat chart="6" format="11" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -17744,6 +17397,54 @@
         </references>
       </pivotArea>
     </chartFormat>
+    <chartFormat chart="0" format="10" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="12" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="11" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="13" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
   </chartFormats>
   <pivotTableStyleInfo name="PivotStyleDark7" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -17757,7 +17458,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3C4F3E9B-F8F0-4C74-AF8B-BEC9DC4B0F54}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="32" rowHeaderCaption="Departments">
   <location ref="A6:C13" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
@@ -17791,7 +17492,7 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0">
       <items count="4">
-        <item x="0"/>
+        <item h="1" x="0"/>
         <item x="1"/>
         <item h="1" x="2"/>
         <item t="default"/>
@@ -17816,22 +17517,22 @@
   </rowFields>
   <rowItems count="7">
     <i>
+      <x v="4"/>
+    </i>
+    <i>
       <x v="2"/>
     </i>
     <i>
       <x v="5"/>
     </i>
     <i>
-      <x v="4"/>
+      <x/>
     </i>
     <i>
       <x v="3"/>
     </i>
     <i>
       <x v="1"/>
-    </i>
-    <i>
-      <x/>
     </i>
     <i t="grand">
       <x/>
@@ -17902,6 +17603,272 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A03E8F95-B095-4BA2-B206-DC1E62353E55}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="15" rowHeaderCaption="Employment Status">
+  <location ref="L32:L33" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="14">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="4"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item h="1" x="0"/>
+        <item x="1"/>
+        <item h="1" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Employee ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="24">
+      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleDark7" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B41A8999-776A-4F6A-A00D-B3164795F990}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="12">
+  <location ref="A33:B36" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="14">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="4"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item h="1" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="9"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of Performance Score" fld="7" subtotal="average" baseField="9" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="25">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="9" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <chartFormats count="3">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="10" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="11" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleDark7" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{61ECD8DF-09A4-4D16-A406-F0081E1DC1AA}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="15" rowHeaderCaption="Employment Status">
+  <location ref="J33:J34" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="14">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="4"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item h="1" x="0"/>
+        <item x="1"/>
+        <item h="1" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Salary" fld="6" baseField="0" baseItem="0" numFmtId="5"/>
+  </dataFields>
+  <formats count="2">
+    <format dxfId="27">
+      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="26">
+      <pivotArea outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleDark7" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_1" connectionId="1" xr16:uid="{5D7FCB3A-69E1-468C-AAC0-C3FE68864305}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
   <queryTableRefresh nextId="21" unboundColumnsRight="4">
@@ -17933,9 +17900,9 @@
     <pivotTable tabId="7" name="PivotTable1"/>
     <pivotTable tabId="7" name="PivotTable10"/>
     <pivotTable tabId="7" name="PivotTable4"/>
-    <pivotTable tabId="7" name="PivotTable9"/>
     <pivotTable tabId="7" name="PivotTable2"/>
     <pivotTable tabId="7" name="PivotTable3"/>
+    <pivotTable tabId="7" name="PivotTable5"/>
   </pivotTables>
   <data>
     <tabular pivotCacheId="1920911821">
@@ -17958,14 +17925,13 @@
     <pivotTable tabId="7" name="PivotTable1"/>
     <pivotTable tabId="7" name="PivotTable10"/>
     <pivotTable tabId="7" name="PivotTable4"/>
-    <pivotTable tabId="7" name="PivotTable9"/>
     <pivotTable tabId="7" name="PivotTable2"/>
     <pivotTable tabId="7" name="PivotTable3"/>
   </pivotTables>
   <data>
     <tabular pivotCacheId="1920911821">
       <items count="3">
-        <i x="0" s="1"/>
+        <i x="0"/>
         <i x="1" s="1"/>
         <i x="2"/>
       </items>
@@ -17980,9 +17946,9 @@
     <pivotTable tabId="7" name="PivotTable1"/>
     <pivotTable tabId="7" name="PivotTable10"/>
     <pivotTable tabId="7" name="PivotTable4"/>
-    <pivotTable tabId="7" name="PivotTable9"/>
     <pivotTable tabId="7" name="PivotTable2"/>
     <pivotTable tabId="7" name="PivotTable3"/>
+    <pivotTable tabId="7" name="PivotTable5"/>
   </pivotTables>
   <data>
     <tabular pivotCacheId="1920911821">
@@ -18420,19 +18386,19 @@
   <dimension ref="A5:L44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.7109375" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="26" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="32.7109375" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="25.5703125" bestFit="1" customWidth="1"/>
   </cols>
@@ -18466,29 +18432,32 @@
         <v>322</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>332</v>
-      </c>
-      <c r="G6" t="s">
         <v>323</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>444</v>
       </c>
       <c r="K6" s="24"/>
       <c r="L6" s="24"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="B7" s="27">
-        <v>34</v>
+        <v>195</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
       </c>
       <c r="C7" s="8">
-        <v>78738.441176470587</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="G7" s="10">
-        <v>0.12142857142857143</v>
+        <v>67739.833333333328</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" t="s">
+        <v>321</v>
       </c>
       <c r="K7" s="6" t="s">
         <v>331</v>
@@ -18499,140 +18468,163 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="B8" s="27">
-        <v>29</v>
+        <v>191</v>
+      </c>
+      <c r="B8">
+        <v>6</v>
       </c>
       <c r="C8" s="8">
-        <v>82899.137931034478</v>
+        <v>81264.833333333328</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="G8" s="10">
-        <v>0.12142857142857143</v>
+        <v>0.125</v>
+      </c>
+      <c r="H8" s="10">
+        <v>0.125</v>
       </c>
       <c r="K8" s="7" t="s">
         <v>203</v>
       </c>
       <c r="L8" s="8">
-        <v>1316600.7999999998</v>
+        <v>169403.2</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="B9" s="27">
-        <v>24</v>
+        <v>194</v>
+      </c>
+      <c r="B9">
+        <v>4</v>
       </c>
       <c r="C9" s="8">
-        <v>75290.416666666672</v>
+        <v>75379.5</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G9" s="10">
-        <v>0.24285714285714285</v>
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="H9" s="10">
+        <v>8.3333333333333329E-2</v>
       </c>
       <c r="K9" s="7" t="s">
         <v>202</v>
       </c>
       <c r="L9" s="8">
-        <v>160371.40000000002</v>
+        <v>41189.799999999996</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="B10" s="27">
-        <v>19</v>
+        <v>192</v>
+      </c>
+      <c r="B10">
+        <v>3</v>
       </c>
       <c r="C10" s="8">
-        <v>84821.263157894733</v>
+        <v>67195</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G10" s="10">
-        <v>0.1357142857142857</v>
+        <v>0.25</v>
+      </c>
+      <c r="H10" s="10">
+        <v>0.25</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="L10" s="8">
-        <v>91073.88</v>
+        <v>10882.46</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="B11" s="27">
-        <v>17</v>
+        <v>193</v>
+      </c>
+      <c r="B11">
+        <v>3</v>
       </c>
       <c r="C11" s="8">
-        <v>86878.76470588235</v>
+        <v>86729</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G11" s="10">
-        <v>0.17142857142857143</v>
+        <v>0.125</v>
+      </c>
+      <c r="H11" s="10">
+        <v>0.125</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L11" s="8">
-        <v>69012.42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="B12" s="27">
-        <v>17</v>
+        <v>190</v>
+      </c>
+      <c r="B12">
+        <v>2</v>
       </c>
       <c r="C12" s="8">
-        <v>85206.470588235301</v>
+        <v>109408</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G12" s="10">
-        <v>0.20714285714285716</v>
+        <v>0.25</v>
+      </c>
+      <c r="H12" s="10">
+        <v>0.25</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>200</v>
+        <v>321</v>
       </c>
       <c r="L12" s="8">
-        <v>0</v>
+        <v>221475.46000000002</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
         <v>321</v>
       </c>
-      <c r="B13" s="27">
-        <v>140</v>
+      <c r="B13">
+        <v>24</v>
       </c>
       <c r="C13" s="8">
-        <v>81608.607142857145</v>
+        <v>78172.25</v>
       </c>
       <c r="F13" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="G13" s="10">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="H13" s="10">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="F14" s="7" t="s">
         <v>321</v>
       </c>
-      <c r="G13" s="10">
+      <c r="G14" s="10">
         <v>1</v>
       </c>
-      <c r="K13" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="L13" s="8">
-        <v>1637058.5</v>
+      <c r="H14" s="10">
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
@@ -18645,54 +18637,54 @@
       <c r="B31" s="25"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B32" t="s">
-        <v>324</v>
-      </c>
       <c r="L32" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B33" s="11">
-        <v>67.577586206896555</v>
+      <c r="A33" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="B33" t="s">
+        <v>324</v>
       </c>
       <c r="J33" t="s">
         <v>340</v>
       </c>
       <c r="L33" s="11">
-        <v>140</v>
+        <v>24</v>
       </c>
     </row>
     <row r="34" spans="1:12" ht="19.5" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B34" s="11">
-        <v>67.25</v>
+        <v>67.577586206896555</v>
       </c>
       <c r="F34" s="21" t="s">
         <v>342</v>
       </c>
       <c r="J34" s="16">
-        <v>11425205</v>
+        <v>1876134</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B35" s="11">
+        <v>67.25</v>
+      </c>
+      <c r="F35" s="19"/>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A36" s="7" t="s">
         <v>321</v>
       </c>
-      <c r="B35" s="11">
+      <c r="B36">
         <v>67.521428571428572</v>
       </c>
-      <c r="F35" s="19"/>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="F36" s="22" t="s">
         <v>336</v>
       </c>
@@ -18713,7 +18705,8 @@
         <v>338</v>
       </c>
       <c r="G40" s="15">
-        <v>0.24</v>
+        <f>GETPIVOTDATA("Employee ID",$F$6,"Department","Information Technology","Employment Status","Left")</f>
+        <v>0.25</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
@@ -19019,7 +19012,7 @@
       </c>
       <c r="G6" t="str">
         <f ca="1">DATEDIF(Cleaned[[#This Row],[Hire Date]], TODAY(), "Y")&amp; "Years"</f>
-        <v>10Years</v>
+        <v>11Years</v>
       </c>
       <c r="H6" s="4">
         <v>65235</v>
@@ -19048,7 +19041,7 @@
       </c>
       <c r="W6" s="2">
         <f ca="1">TODAY()</f>
-        <v>46209</v>
+        <v>46210</v>
       </c>
     </row>
     <row r="7" spans="2:23" x14ac:dyDescent="0.25">
